--- a/data/stx_xlsx/MTRS.ST.xlsx
+++ b/data/stx_xlsx/MTRS.ST.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="688" uniqueCount="424">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="688" uniqueCount="425">
   <si>
     <t>Company Fundamentals - Income Statement</t>
   </si>
@@ -859,6 +859,9 @@
   </si>
   <si>
     <t>Total Non-Current Liabilities</t>
+  </si>
+  <si>
+    <t>Interest-bearing liabilities (Do not use)</t>
   </si>
   <si>
     <t>Interest-bearing liabilities - Balancing value</t>
@@ -1416,7 +1419,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="34">
+  <cellXfs count="35">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -1494,6 +1497,9 @@
     </xf>
     <xf borderId="3" fillId="0" fontId="6" numFmtId="4" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="left" shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
+    <xf borderId="3" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
     <xf borderId="3" fillId="3" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="left" shrinkToFit="0" vertical="center" wrapText="1"/>
@@ -11235,8 +11241,8 @@
       </c>
     </row>
     <row r="122" ht="15.0" customHeight="1">
-      <c r="A122" s="14" t="s">
-        <v>272</v>
+      <c r="A122" s="26" t="s">
+        <v>280</v>
       </c>
       <c r="B122" s="15"/>
       <c r="C122" s="15"/>
@@ -11269,7 +11275,7 @@
     </row>
     <row r="123" ht="15.0" customHeight="1">
       <c r="A123" s="14" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="B123" s="15"/>
       <c r="C123" s="15"/>
@@ -11291,8 +11297,8 @@
       <c r="M123" s="15"/>
     </row>
     <row r="124" ht="15.0" customHeight="1">
-      <c r="A124" s="14" t="s">
-        <v>272</v>
+      <c r="A124" s="26" t="s">
+        <v>280</v>
       </c>
       <c r="B124" s="16">
         <v>906.48</v>
@@ -11317,7 +11323,7 @@
     </row>
     <row r="125" ht="15.0" customHeight="1">
       <c r="A125" s="14" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="B125" s="16">
         <v>306.17</v>
@@ -11348,7 +11354,7 @@
     </row>
     <row r="126" ht="15.0" customHeight="1">
       <c r="A126" s="14" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="B126" s="15"/>
       <c r="C126" s="15"/>
@@ -11422,7 +11428,7 @@
     </row>
     <row r="128" ht="15.0" customHeight="1">
       <c r="A128" s="14" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="B128" s="16">
         <v>1597.55</v>
@@ -11463,7 +11469,7 @@
     </row>
     <row r="129" ht="15.0" customHeight="1">
       <c r="A129" s="14" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="B129" s="20">
         <v>84.2</v>
@@ -11504,7 +11510,7 @@
     </row>
     <row r="130" ht="15.0" customHeight="1">
       <c r="A130" s="14" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="B130" s="16">
         <v>2692.11</v>
@@ -11545,7 +11551,7 @@
     </row>
     <row r="131" ht="15.0" customHeight="1">
       <c r="A131" s="14" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="B131" s="16">
         <v>394.74</v>
@@ -11586,7 +11592,7 @@
     </row>
     <row r="132" ht="15.0" customHeight="1">
       <c r="A132" s="14" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="B132" s="16">
         <v>1088.0</v>
@@ -11627,7 +11633,7 @@
     </row>
     <row r="133" ht="15.0" customHeight="1">
       <c r="A133" s="14" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="B133" s="20">
         <v>17.5</v>
@@ -11668,7 +11674,7 @@
     </row>
     <row r="134" ht="15.0" customHeight="1">
       <c r="A134" s="14" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="B134" s="16">
         <v>612.34</v>
@@ -11709,7 +11715,7 @@
     </row>
     <row r="135" ht="15.0" customHeight="1">
       <c r="A135" s="14" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="B135" s="20">
         <v>55.77</v>
@@ -11742,7 +11748,7 @@
     </row>
     <row r="136" ht="15.0" customHeight="1">
       <c r="A136" s="14" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="B136" s="16">
         <v>402.4</v>
@@ -11824,7 +11830,7 @@
     </row>
     <row r="138" ht="15.0" customHeight="1">
       <c r="A138" s="14" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="B138" s="15"/>
       <c r="C138" s="21">
@@ -11847,7 +11853,7 @@
     </row>
     <row r="139" ht="15.0" customHeight="1">
       <c r="A139" s="17" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="B139" s="19">
         <v>7304.36</v>
@@ -11888,7 +11894,7 @@
     </row>
     <row r="140" ht="15.0" customHeight="1">
       <c r="A140" s="17" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="B140" s="18">
         <v>16251.1</v>
@@ -11929,7 +11935,7 @@
     </row>
     <row r="141" ht="15.0" customHeight="1">
       <c r="A141" s="14" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="B141" s="15"/>
       <c r="C141" s="15"/>
@@ -11956,7 +11962,7 @@
     </row>
     <row r="142" ht="15.0" customHeight="1">
       <c r="A142" s="17" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="B142" s="18">
         <v>21571.91</v>
@@ -11997,7 +12003,7 @@
     </row>
     <row r="143" ht="15.0" customHeight="1">
       <c r="A143" s="14" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="B143" s="20">
         <v>1.92</v>
@@ -12038,7 +12044,7 @@
     </row>
     <row r="144" ht="15.0" customHeight="1">
       <c r="A144" s="14" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="B144" s="16">
         <v>182.54</v>
@@ -12079,7 +12085,7 @@
     </row>
     <row r="145" ht="15.0" customHeight="1">
       <c r="A145" s="14" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="B145" s="16">
         <v>184.46</v>
@@ -12120,7 +12126,7 @@
     </row>
     <row r="146" ht="15.0" customHeight="1">
       <c r="A146" s="14" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="B146" s="15"/>
       <c r="C146" s="15"/>
@@ -12145,7 +12151,7 @@
     </row>
     <row r="147" ht="15.0" customHeight="1">
       <c r="A147" s="14" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="B147" s="15"/>
       <c r="C147" s="15"/>
@@ -12170,7 +12176,7 @@
     </row>
     <row r="148" ht="15.0" customHeight="1">
       <c r="A148" s="14" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="B148" s="15"/>
       <c r="C148" s="15"/>
@@ -12195,7 +12201,7 @@
     </row>
     <row r="149" ht="15.0" customHeight="1">
       <c r="A149" s="14" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="B149" s="15"/>
       <c r="C149" s="15"/>
@@ -12220,7 +12226,7 @@
     </row>
     <row r="150" ht="15.0" customHeight="1">
       <c r="A150" s="14" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="B150" s="15"/>
       <c r="C150" s="15"/>
@@ -12239,7 +12245,7 @@
     </row>
     <row r="151" ht="15.0" customHeight="1">
       <c r="A151" s="14" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="B151" s="16">
         <v>331.32</v>
@@ -12262,7 +12268,7 @@
     </row>
     <row r="152" ht="15.0" customHeight="1">
       <c r="A152" s="14" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="B152" s="16">
         <v>1030.05</v>
@@ -12285,7 +12291,7 @@
     </row>
     <row r="153" ht="15.0" customHeight="1">
       <c r="A153" s="14" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="B153" s="16">
         <v>1483.83</v>
@@ -12308,7 +12314,7 @@
     </row>
     <row r="154" ht="15.0" customHeight="1">
       <c r="A154" s="14" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="B154" s="15"/>
       <c r="C154" s="16">
@@ -12329,7 +12335,7 @@
     </row>
     <row r="155" ht="15.0" customHeight="1">
       <c r="A155" s="14" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="B155" s="16">
         <v>182.54</v>
@@ -12370,7 +12376,7 @@
     </row>
     <row r="156" ht="15.0" customHeight="1">
       <c r="A156" s="14" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="B156" s="20">
         <v>1.92</v>
@@ -12411,7 +12417,7 @@
     </row>
     <row r="157" ht="15.0" customHeight="1">
       <c r="A157" s="14" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="B157" s="16">
         <v>184.46</v>
@@ -12452,7 +12458,7 @@
     </row>
     <row r="158" ht="15.0" customHeight="1">
       <c r="A158" s="14" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="B158" s="20">
         <v>1.0</v>
@@ -12493,7 +12499,7 @@
     </row>
     <row r="159" ht="15.0" customHeight="1">
       <c r="A159" s="14" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="B159" s="16">
         <v>4990.0</v>
@@ -12534,7 +12540,7 @@
     </row>
     <row r="160" ht="15.0" customHeight="1">
       <c r="A160" s="14" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="B160" s="15"/>
       <c r="C160" s="15"/>
@@ -12561,7 +12567,7 @@
     </row>
     <row r="161" ht="15.0" customHeight="1">
       <c r="A161" s="14" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="B161" s="15"/>
       <c r="C161" s="15"/>
@@ -12588,7 +12594,7 @@
     </row>
     <row r="162" ht="15.0" customHeight="1">
       <c r="A162" s="14" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="B162" s="15"/>
       <c r="C162" s="15"/>
@@ -12615,7 +12621,7 @@
     </row>
     <row r="163" ht="15.0" customHeight="1">
       <c r="A163" s="14" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="B163" s="15"/>
       <c r="C163" s="15"/>
@@ -12642,7 +12648,7 @@
     </row>
     <row r="164" ht="15.0" customHeight="1">
       <c r="A164" s="14" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="B164" s="15">
         <v>20866.0</v>
@@ -12677,7 +12683,7 @@
     </row>
     <row r="165" ht="15.0" customHeight="1">
       <c r="A165" s="14" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="B165" s="15">
         <v>18897.29</v>
@@ -13567,7 +13573,7 @@
   <sheetData>
     <row r="1" ht="15.0" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -13823,40 +13829,40 @@
         <v>34</v>
       </c>
       <c r="B15" s="10" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="C15" s="10" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="D15" s="10" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="E15" s="10" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="F15" s="10" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="G15" s="10" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="H15" s="10" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="I15" s="10" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="J15" s="10" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="K15" s="10" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="L15" s="10" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="M15" s="10" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
     </row>
     <row r="16" ht="15.0" customHeight="1" outlineLevel="1">
@@ -13902,7 +13908,7 @@
     </row>
     <row r="18">
       <c r="A18" s="12" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="B18" s="6"/>
       <c r="C18" s="6"/>
@@ -13960,7 +13966,7 @@
     </row>
     <row r="20" ht="15.0" customHeight="1">
       <c r="A20" s="14" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="B20" s="16">
         <v>795.43</v>
@@ -13979,7 +13985,7 @@
     </row>
     <row r="21" ht="15.0" customHeight="1">
       <c r="A21" s="14" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="B21" s="16">
         <v>1560.15</v>
@@ -14051,7 +14057,7 @@
     </row>
     <row r="23" ht="15.0" customHeight="1">
       <c r="A23" s="14" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="B23" s="15"/>
       <c r="C23" s="16">
@@ -14090,7 +14096,7 @@
     </row>
     <row r="24" ht="15.0" customHeight="1">
       <c r="A24" s="14" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="B24" s="16">
         <v>231.96</v>
@@ -14131,7 +14137,7 @@
     </row>
     <row r="25" ht="15.0" customHeight="1">
       <c r="A25" s="14" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="B25" s="20">
         <v>8.47</v>
@@ -14172,7 +14178,7 @@
     </row>
     <row r="26" ht="15.0" customHeight="1">
       <c r="A26" s="14" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="B26" s="23">
         <v>-420.49</v>
@@ -14213,7 +14219,7 @@
     </row>
     <row r="27" ht="15.0" customHeight="1">
       <c r="A27" s="14" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="B27" s="23">
         <v>-354.82</v>
@@ -14254,7 +14260,7 @@
     </row>
     <row r="28" ht="15.0" customHeight="1">
       <c r="A28" s="14" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="B28" s="15"/>
       <c r="C28" s="15"/>
@@ -14273,7 +14279,7 @@
     </row>
     <row r="29" ht="15.0" customHeight="1">
       <c r="A29" s="14" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="B29" s="16">
         <v>822.97</v>
@@ -14308,7 +14314,7 @@
     </row>
     <row r="30" ht="15.0" customHeight="1">
       <c r="A30" s="14" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="B30" s="15"/>
       <c r="C30" s="15"/>
@@ -14331,7 +14337,7 @@
     </row>
     <row r="31" ht="15.0" customHeight="1">
       <c r="A31" s="14" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="B31" s="16">
         <v>240.43</v>
@@ -14368,7 +14374,7 @@
     </row>
     <row r="32" ht="15.0" customHeight="1">
       <c r="A32" s="14" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="B32" s="23">
         <v>-114.39</v>
@@ -14405,7 +14411,7 @@
     </row>
     <row r="33" ht="15.0" customHeight="1">
       <c r="A33" s="14" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="B33" s="23">
         <v>-402.48</v>
@@ -14436,7 +14442,7 @@
     </row>
     <row r="34" ht="15.0" customHeight="1">
       <c r="A34" s="14" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="B34" s="20">
         <v>66.73</v>
@@ -14473,7 +14479,7 @@
     </row>
     <row r="35" ht="15.0" customHeight="1">
       <c r="A35" s="14" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="B35" s="16">
         <v>1031.62</v>
@@ -14510,7 +14516,7 @@
     </row>
     <row r="36" ht="15.0" customHeight="1">
       <c r="A36" s="14" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="B36" s="23">
         <v>-563.47</v>
@@ -14541,7 +14547,7 @@
     </row>
     <row r="37" ht="15.0" customHeight="1">
       <c r="A37" s="14" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="B37" s="23">
         <v>-146.16</v>
@@ -14560,7 +14566,7 @@
     </row>
     <row r="38" ht="15.0" customHeight="1">
       <c r="A38" s="14" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="B38" s="15"/>
       <c r="C38" s="15"/>
@@ -14583,7 +14589,7 @@
     </row>
     <row r="39" ht="15.0" customHeight="1">
       <c r="A39" s="14" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="B39" s="15"/>
       <c r="C39" s="21">
@@ -14612,7 +14618,7 @@
     </row>
     <row r="40" ht="15.0" customHeight="1">
       <c r="A40" s="17" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="B40" s="19">
         <v>1673.48</v>
@@ -14653,7 +14659,7 @@
     </row>
     <row r="41" ht="15.0" customHeight="1">
       <c r="A41" s="14" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="B41" s="23">
         <v>-1218.04</v>
@@ -14694,7 +14700,7 @@
     </row>
     <row r="42" ht="15.0" customHeight="1">
       <c r="A42" s="14" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="B42" s="15"/>
       <c r="C42" s="21">
@@ -14717,7 +14723,7 @@
     </row>
     <row r="43" ht="15.0" customHeight="1">
       <c r="A43" s="14" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="B43" s="21">
         <v>-23.3</v>
@@ -14742,7 +14748,7 @@
     </row>
     <row r="44" ht="15.0" customHeight="1">
       <c r="A44" s="14" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="B44" s="15"/>
       <c r="C44" s="20">
@@ -14765,7 +14771,7 @@
     </row>
     <row r="45" ht="15.0" customHeight="1">
       <c r="A45" s="14" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="B45" s="15"/>
       <c r="C45" s="15"/>
@@ -14796,7 +14802,7 @@
     </row>
     <row r="46" ht="15.0" customHeight="1">
       <c r="A46" s="14" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="B46" s="23">
         <v>-627.02</v>
@@ -14837,7 +14843,7 @@
     </row>
     <row r="47" ht="15.0" customHeight="1">
       <c r="A47" s="14" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="B47" s="23">
         <v>-281.74</v>
@@ -14878,7 +14884,7 @@
     </row>
     <row r="48" ht="15.0" customHeight="1">
       <c r="A48" s="14" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="B48" s="15"/>
       <c r="C48" s="15"/>
@@ -14911,7 +14917,7 @@
     </row>
     <row r="49" ht="15.0" customHeight="1">
       <c r="A49" s="14" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="B49" s="16">
         <v>1080.35</v>
@@ -14930,7 +14936,7 @@
     </row>
     <row r="50" ht="15.0" customHeight="1">
       <c r="A50" s="14" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="B50" s="15"/>
       <c r="C50" s="15"/>
@@ -14951,7 +14957,7 @@
     </row>
     <row r="51" ht="15.0" customHeight="1">
       <c r="A51" s="14" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="B51" s="21">
         <v>-1.06</v>
@@ -14980,7 +14986,7 @@
     </row>
     <row r="52" ht="15.0" customHeight="1">
       <c r="A52" s="17" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="B52" s="24">
         <v>-1070.81</v>
@@ -15021,7 +15027,7 @@
     </row>
     <row r="53" ht="15.0" customHeight="1">
       <c r="A53" s="14" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="B53" s="15"/>
       <c r="C53" s="15"/>
@@ -15042,7 +15048,7 @@
     </row>
     <row r="54" ht="15.0" customHeight="1">
       <c r="A54" s="14" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="B54" s="15"/>
       <c r="C54" s="15"/>
@@ -15067,7 +15073,7 @@
     </row>
     <row r="55" ht="15.0" customHeight="1">
       <c r="A55" s="14" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="B55" s="15">
         <v>0.0</v>
@@ -15096,7 +15102,7 @@
     </row>
     <row r="56" ht="15.0" customHeight="1">
       <c r="A56" s="14" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="B56" s="16">
         <v>8870.49</v>
@@ -15137,7 +15143,7 @@
     </row>
     <row r="57" ht="15.0" customHeight="1">
       <c r="A57" s="14" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="B57" s="23">
         <v>-8727.5</v>
@@ -15178,7 +15184,7 @@
     </row>
     <row r="58" ht="15.0" customHeight="1">
       <c r="A58" s="14" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="B58" s="23">
         <v>-213.95</v>
@@ -15209,7 +15215,7 @@
     </row>
     <row r="59" ht="15.0" customHeight="1">
       <c r="A59" s="14" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="B59" s="15"/>
       <c r="C59" s="15"/>
@@ -15236,7 +15242,7 @@
     </row>
     <row r="60" ht="15.0" customHeight="1">
       <c r="A60" s="14" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="B60" s="23">
         <v>-309.28</v>
@@ -15269,7 +15275,7 @@
     </row>
     <row r="61" ht="15.0" customHeight="1">
       <c r="A61" s="14" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="B61" s="21">
         <v>-16.95</v>
@@ -15298,7 +15304,7 @@
     </row>
     <row r="62" ht="15.0" customHeight="1">
       <c r="A62" s="14" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="B62" s="21">
         <v>-92.15</v>
@@ -15323,7 +15329,7 @@
     </row>
     <row r="63" ht="15.0" customHeight="1">
       <c r="A63" s="14" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="B63" s="21">
         <v>-10.59</v>
@@ -15342,7 +15348,7 @@
     </row>
     <row r="64" ht="15.0" customHeight="1">
       <c r="A64" s="14" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="B64" s="15"/>
       <c r="C64" s="15"/>
@@ -15365,7 +15371,7 @@
     </row>
     <row r="65" ht="15.0" customHeight="1">
       <c r="A65" s="14" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="B65" s="15"/>
       <c r="C65" s="15"/>
@@ -15388,7 +15394,7 @@
     </row>
     <row r="66" ht="15.0" customHeight="1">
       <c r="A66" s="14" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="B66" s="20">
         <v>1.06</v>
@@ -15419,7 +15425,7 @@
     </row>
     <row r="67" ht="15.0" customHeight="1">
       <c r="A67" s="17" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="B67" s="24">
         <v>-498.87</v>
@@ -15460,7 +15466,7 @@
     </row>
     <row r="68" ht="15.0" customHeight="1">
       <c r="A68" s="14" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="B68" s="16">
         <v>1673.0</v>
@@ -15501,7 +15507,7 @@
     </row>
     <row r="69" ht="15.0" customHeight="1">
       <c r="A69" s="14" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="B69" s="16">
         <v>1631.45</v>
@@ -15542,7 +15548,7 @@
     </row>
     <row r="70" ht="15.0" customHeight="1">
       <c r="A70" s="14" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="B70" s="23">
         <v>-142.99</v>
@@ -15583,7 +15589,7 @@
     </row>
     <row r="71" ht="15.0" customHeight="1">
       <c r="A71" s="14" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="B71" s="16">
         <v>103.8</v>
@@ -15618,7 +15624,7 @@
     </row>
     <row r="72" ht="15.0" customHeight="1">
       <c r="A72" s="17" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="B72" s="22">
         <v>-39.19</v>
@@ -16607,7 +16613,7 @@
   <sheetData>
     <row r="1" ht="15.0" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -16942,7 +16948,7 @@
     </row>
     <row r="18">
       <c r="A18" s="12" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="B18" s="6"/>
       <c r="C18" s="6"/>
@@ -16999,1330 +17005,1330 @@
       </c>
     </row>
     <row r="20" ht="15.0" customHeight="1">
-      <c r="A20" s="26" t="s">
-        <v>376</v>
-      </c>
-      <c r="B20" s="27"/>
-      <c r="C20" s="27"/>
-      <c r="D20" s="27"/>
-      <c r="E20" s="27"/>
-      <c r="F20" s="27"/>
-      <c r="G20" s="27"/>
-      <c r="H20" s="27"/>
-      <c r="I20" s="27"/>
-      <c r="J20" s="27"/>
-      <c r="K20" s="27"/>
-      <c r="L20" s="27"/>
-      <c r="M20" s="27"/>
+      <c r="A20" s="27" t="s">
+        <v>377</v>
+      </c>
+      <c r="B20" s="28"/>
+      <c r="C20" s="28"/>
+      <c r="D20" s="28"/>
+      <c r="E20" s="28"/>
+      <c r="F20" s="28"/>
+      <c r="G20" s="28"/>
+      <c r="H20" s="28"/>
+      <c r="I20" s="28"/>
+      <c r="J20" s="28"/>
+      <c r="K20" s="28"/>
+      <c r="L20" s="28"/>
+      <c r="M20" s="28"/>
     </row>
     <row r="21" ht="15.0" customHeight="1">
-      <c r="A21" s="28" t="s">
-        <v>376</v>
-      </c>
-      <c r="B21" s="29">
+      <c r="A21" s="29" t="s">
+        <v>377</v>
+      </c>
+      <c r="B21" s="30">
         <v>41708.43</v>
       </c>
-      <c r="C21" s="29">
+      <c r="C21" s="30">
         <v>41525.97</v>
       </c>
-      <c r="D21" s="29">
+      <c r="D21" s="30">
         <v>34712.09</v>
       </c>
-      <c r="E21" s="29">
+      <c r="E21" s="30">
         <v>21240.32</v>
       </c>
-      <c r="F21" s="29">
+      <c r="F21" s="30">
         <v>14596.47</v>
       </c>
-      <c r="G21" s="29">
+      <c r="G21" s="30">
         <v>17889.25</v>
       </c>
-      <c r="H21" s="29">
+      <c r="H21" s="30">
         <v>11047.83</v>
       </c>
-      <c r="I21" s="30">
+      <c r="I21" s="31">
         <v>8633.75</v>
       </c>
-      <c r="J21" s="29">
+      <c r="J21" s="30">
         <v>12604.92</v>
       </c>
-      <c r="K21" s="29"/>
-      <c r="L21" s="29"/>
-      <c r="M21" s="29"/>
+      <c r="K21" s="30"/>
+      <c r="L21" s="30"/>
+      <c r="M21" s="30"/>
     </row>
     <row r="22" ht="15.0" customHeight="1">
-      <c r="A22" s="28" t="s">
-        <v>377</v>
-      </c>
-      <c r="B22" s="29">
+      <c r="A22" s="29" t="s">
+        <v>378</v>
+      </c>
+      <c r="B22" s="30">
         <v>32926.65</v>
       </c>
-      <c r="C22" s="29">
+      <c r="C22" s="30">
         <v>26637.86</v>
       </c>
-      <c r="D22" s="29">
+      <c r="D22" s="30">
         <v>20324.7</v>
       </c>
-      <c r="E22" s="29">
+      <c r="E22" s="30">
         <v>14177.18</v>
       </c>
-      <c r="F22" s="29">
+      <c r="F22" s="30">
         <v>12731.92</v>
       </c>
-      <c r="G22" s="29"/>
-      <c r="H22" s="29"/>
-      <c r="I22" s="29"/>
-      <c r="J22" s="29"/>
-      <c r="K22" s="29"/>
-      <c r="L22" s="29"/>
-      <c r="M22" s="29"/>
+      <c r="G22" s="30"/>
+      <c r="H22" s="30"/>
+      <c r="I22" s="30"/>
+      <c r="J22" s="30"/>
+      <c r="K22" s="30"/>
+      <c r="L22" s="30"/>
+      <c r="M22" s="30"/>
     </row>
     <row r="23" ht="15.0" customHeight="1">
-      <c r="A23" s="26" t="s">
-        <v>378</v>
-      </c>
-      <c r="B23" s="27"/>
-      <c r="C23" s="27"/>
-      <c r="D23" s="27"/>
-      <c r="E23" s="27"/>
-      <c r="F23" s="27"/>
-      <c r="G23" s="27"/>
-      <c r="H23" s="27"/>
-      <c r="I23" s="27"/>
-      <c r="J23" s="27"/>
-      <c r="K23" s="27"/>
-      <c r="L23" s="27"/>
-      <c r="M23" s="27"/>
+      <c r="A23" s="27" t="s">
+        <v>379</v>
+      </c>
+      <c r="B23" s="28"/>
+      <c r="C23" s="28"/>
+      <c r="D23" s="28"/>
+      <c r="E23" s="28"/>
+      <c r="F23" s="28"/>
+      <c r="G23" s="28"/>
+      <c r="H23" s="28"/>
+      <c r="I23" s="28"/>
+      <c r="J23" s="28"/>
+      <c r="K23" s="28"/>
+      <c r="L23" s="28"/>
+      <c r="M23" s="28"/>
     </row>
     <row r="24" ht="15.0" customHeight="1">
-      <c r="A24" s="28" t="s">
-        <v>378</v>
-      </c>
-      <c r="B24" s="29">
+      <c r="A24" s="29" t="s">
+        <v>379</v>
+      </c>
+      <c r="B24" s="30">
         <v>34671.97</v>
       </c>
-      <c r="C24" s="29">
+      <c r="C24" s="30">
         <v>35273.09</v>
       </c>
-      <c r="D24" s="29">
+      <c r="D24" s="30">
         <v>30362.87</v>
       </c>
-      <c r="E24" s="29">
+      <c r="E24" s="30">
         <v>17865.88</v>
       </c>
-      <c r="F24" s="29">
+      <c r="F24" s="30">
         <v>12570.95</v>
       </c>
-      <c r="G24" s="29">
+      <c r="G24" s="30">
         <v>15986.71</v>
       </c>
-      <c r="H24" s="30">
+      <c r="H24" s="31">
         <v>8445.82</v>
       </c>
-      <c r="I24" s="30">
+      <c r="I24" s="31">
         <v>6091.63</v>
       </c>
-      <c r="J24" s="29">
+      <c r="J24" s="30">
         <v>10150.33</v>
       </c>
-      <c r="K24" s="29"/>
-      <c r="L24" s="29"/>
-      <c r="M24" s="29"/>
+      <c r="K24" s="30"/>
+      <c r="L24" s="30"/>
+      <c r="M24" s="30"/>
     </row>
     <row r="25" ht="15.0" customHeight="1">
-      <c r="A25" s="28" t="s">
-        <v>379</v>
-      </c>
-      <c r="B25" s="29">
+      <c r="A25" s="29" t="s">
+        <v>380</v>
+      </c>
+      <c r="B25" s="30">
         <v>28005.83</v>
       </c>
-      <c r="C25" s="29">
+      <c r="C25" s="30">
         <v>22959.75</v>
       </c>
-      <c r="D25" s="29">
+      <c r="D25" s="30">
         <v>17388.78</v>
       </c>
-      <c r="E25" s="29">
+      <c r="E25" s="30">
         <v>11755.12</v>
       </c>
-      <c r="F25" s="29">
+      <c r="F25" s="30">
         <v>10445.48</v>
       </c>
-      <c r="G25" s="29"/>
-      <c r="H25" s="29"/>
-      <c r="I25" s="29"/>
-      <c r="J25" s="29"/>
-      <c r="K25" s="29"/>
-      <c r="L25" s="29"/>
-      <c r="M25" s="29"/>
+      <c r="G25" s="30"/>
+      <c r="H25" s="30"/>
+      <c r="I25" s="30"/>
+      <c r="J25" s="30"/>
+      <c r="K25" s="30"/>
+      <c r="L25" s="30"/>
+      <c r="M25" s="30"/>
     </row>
     <row r="26" ht="15.0" customHeight="1">
-      <c r="A26" s="26" t="s">
-        <v>380</v>
-      </c>
-      <c r="B26" s="27"/>
-      <c r="C26" s="27"/>
-      <c r="D26" s="27"/>
-      <c r="E26" s="27"/>
-      <c r="F26" s="27"/>
-      <c r="G26" s="27"/>
-      <c r="H26" s="27"/>
-      <c r="I26" s="27"/>
-      <c r="J26" s="27"/>
-      <c r="K26" s="27"/>
-      <c r="L26" s="27"/>
-      <c r="M26" s="27"/>
+      <c r="A26" s="27" t="s">
+        <v>381</v>
+      </c>
+      <c r="B26" s="28"/>
+      <c r="C26" s="28"/>
+      <c r="D26" s="28"/>
+      <c r="E26" s="28"/>
+      <c r="F26" s="28"/>
+      <c r="G26" s="28"/>
+      <c r="H26" s="28"/>
+      <c r="I26" s="28"/>
+      <c r="J26" s="28"/>
+      <c r="K26" s="28"/>
+      <c r="L26" s="28"/>
+      <c r="M26" s="28"/>
     </row>
     <row r="27" ht="15.0" customHeight="1">
-      <c r="A27" s="28" t="s">
-        <v>381</v>
-      </c>
-      <c r="B27" s="30">
+      <c r="A27" s="29" t="s">
+        <v>382</v>
+      </c>
+      <c r="B27" s="31">
         <v>187.97</v>
       </c>
-      <c r="C27" s="30">
+      <c r="C27" s="31">
         <v>191.23</v>
       </c>
-      <c r="D27" s="30">
+      <c r="D27" s="31">
         <v>164.61</v>
       </c>
-      <c r="E27" s="31">
+      <c r="E27" s="32">
         <v>96.86</v>
       </c>
-      <c r="F27" s="31">
+      <c r="F27" s="32">
         <v>68.15</v>
       </c>
-      <c r="G27" s="31">
+      <c r="G27" s="32">
         <v>86.67</v>
       </c>
-      <c r="H27" s="31">
+      <c r="H27" s="32">
         <v>46.0</v>
       </c>
-      <c r="I27" s="31">
+      <c r="I27" s="32">
         <v>33.18</v>
       </c>
-      <c r="J27" s="31">
+      <c r="J27" s="32">
         <v>55.29</v>
       </c>
-      <c r="K27" s="29"/>
-      <c r="L27" s="29"/>
-      <c r="M27" s="29"/>
+      <c r="K27" s="30"/>
+      <c r="L27" s="30"/>
+      <c r="M27" s="30"/>
     </row>
     <row r="28" ht="15.0" customHeight="1">
-      <c r="A28" s="28" t="s">
-        <v>382</v>
-      </c>
-      <c r="B28" s="30">
+      <c r="A28" s="29" t="s">
+        <v>383</v>
+      </c>
+      <c r="B28" s="31">
         <v>151.83</v>
       </c>
-      <c r="C28" s="30">
+      <c r="C28" s="31">
         <v>124.47</v>
       </c>
-      <c r="D28" s="31">
+      <c r="D28" s="32">
         <v>94.32</v>
       </c>
-      <c r="E28" s="31">
+      <c r="E28" s="32">
         <v>63.8</v>
       </c>
-      <c r="F28" s="31">
+      <c r="F28" s="32">
         <v>56.75</v>
       </c>
-      <c r="G28" s="29"/>
-      <c r="H28" s="29"/>
-      <c r="I28" s="29"/>
-      <c r="J28" s="29"/>
-      <c r="K28" s="29"/>
-      <c r="L28" s="29"/>
-      <c r="M28" s="29"/>
+      <c r="G28" s="30"/>
+      <c r="H28" s="30"/>
+      <c r="I28" s="30"/>
+      <c r="J28" s="30"/>
+      <c r="K28" s="30"/>
+      <c r="L28" s="30"/>
+      <c r="M28" s="30"/>
     </row>
     <row r="29" ht="15.0" customHeight="1">
-      <c r="A29" s="26" t="s">
-        <v>383</v>
-      </c>
-      <c r="B29" s="27"/>
-      <c r="C29" s="27"/>
-      <c r="D29" s="27"/>
-      <c r="E29" s="27"/>
-      <c r="F29" s="27"/>
-      <c r="G29" s="27"/>
-      <c r="H29" s="27"/>
-      <c r="I29" s="27"/>
-      <c r="J29" s="27"/>
-      <c r="K29" s="27"/>
-      <c r="L29" s="27"/>
-      <c r="M29" s="27"/>
+      <c r="A29" s="27" t="s">
+        <v>384</v>
+      </c>
+      <c r="B29" s="28"/>
+      <c r="C29" s="28"/>
+      <c r="D29" s="28"/>
+      <c r="E29" s="28"/>
+      <c r="F29" s="28"/>
+      <c r="G29" s="28"/>
+      <c r="H29" s="28"/>
+      <c r="I29" s="28"/>
+      <c r="J29" s="28"/>
+      <c r="K29" s="28"/>
+      <c r="L29" s="28"/>
+      <c r="M29" s="28"/>
     </row>
     <row r="30" ht="15.0" customHeight="1">
-      <c r="A30" s="28" t="s">
-        <v>384</v>
-      </c>
-      <c r="B30" s="32">
+      <c r="A30" s="29" t="s">
+        <v>385</v>
+      </c>
+      <c r="B30" s="33">
         <v>2.74</v>
       </c>
-      <c r="C30" s="32">
+      <c r="C30" s="33">
         <v>3.85</v>
       </c>
-      <c r="D30" s="32">
+      <c r="D30" s="33">
         <v>1.33</v>
       </c>
-      <c r="E30" s="32">
+      <c r="E30" s="33">
         <v>1.24</v>
       </c>
-      <c r="F30" s="32">
+      <c r="F30" s="33">
         <v>1.39</v>
       </c>
-      <c r="G30" s="32">
+      <c r="G30" s="33">
         <v>4.92</v>
       </c>
-      <c r="H30" s="32">
+      <c r="H30" s="33">
         <v>5.32</v>
       </c>
-      <c r="I30" s="32">
+      <c r="I30" s="33">
         <v>3.36</v>
       </c>
-      <c r="J30" s="32">
+      <c r="J30" s="33">
         <v>0.98</v>
       </c>
-      <c r="K30" s="32"/>
-      <c r="L30" s="32"/>
-      <c r="M30" s="32"/>
+      <c r="K30" s="33"/>
+      <c r="L30" s="33"/>
+      <c r="M30" s="33"/>
     </row>
     <row r="31" ht="15.0" customHeight="1">
-      <c r="A31" s="28" t="s">
-        <v>385</v>
-      </c>
-      <c r="B31" s="32">
+      <c r="A31" s="29" t="s">
+        <v>386</v>
+      </c>
+      <c r="B31" s="33">
         <v>2.35</v>
       </c>
-      <c r="C31" s="32">
+      <c r="C31" s="33">
         <v>2.59</v>
       </c>
-      <c r="D31" s="32">
+      <c r="D31" s="33">
         <v>2.37</v>
       </c>
-      <c r="E31" s="32">
+      <c r="E31" s="33">
         <v>2.98</v>
       </c>
-      <c r="F31" s="32">
+      <c r="F31" s="33">
         <v>3.21</v>
       </c>
-      <c r="G31" s="32"/>
-      <c r="H31" s="32"/>
-      <c r="I31" s="32"/>
-      <c r="J31" s="32"/>
-      <c r="K31" s="32"/>
-      <c r="L31" s="32"/>
-      <c r="M31" s="32"/>
+      <c r="G31" s="33"/>
+      <c r="H31" s="33"/>
+      <c r="I31" s="33"/>
+      <c r="J31" s="33"/>
+      <c r="K31" s="33"/>
+      <c r="L31" s="33"/>
+      <c r="M31" s="33"/>
     </row>
     <row r="32" ht="15.0" customHeight="1">
-      <c r="A32" s="26" t="s">
-        <v>386</v>
-      </c>
-      <c r="B32" s="27"/>
-      <c r="C32" s="27"/>
-      <c r="D32" s="27"/>
-      <c r="E32" s="27"/>
-      <c r="F32" s="27"/>
-      <c r="G32" s="27"/>
-      <c r="H32" s="27"/>
-      <c r="I32" s="27"/>
-      <c r="J32" s="27"/>
-      <c r="K32" s="27"/>
-      <c r="L32" s="27"/>
-      <c r="M32" s="27"/>
+      <c r="A32" s="27" t="s">
+        <v>387</v>
+      </c>
+      <c r="B32" s="28"/>
+      <c r="C32" s="28"/>
+      <c r="D32" s="28"/>
+      <c r="E32" s="28"/>
+      <c r="F32" s="28"/>
+      <c r="G32" s="28"/>
+      <c r="H32" s="28"/>
+      <c r="I32" s="28"/>
+      <c r="J32" s="28"/>
+      <c r="K32" s="28"/>
+      <c r="L32" s="28"/>
+      <c r="M32" s="28"/>
     </row>
     <row r="33" ht="15.0" customHeight="1">
-      <c r="A33" s="28" t="s">
-        <v>387</v>
-      </c>
-      <c r="B33" s="32">
+      <c r="A33" s="29" t="s">
+        <v>388</v>
+      </c>
+      <c r="B33" s="33">
         <v>0.65</v>
       </c>
-      <c r="C33" s="32">
+      <c r="C33" s="33">
         <v>0.73</v>
       </c>
-      <c r="D33" s="32">
+      <c r="D33" s="33">
         <v>0.41</v>
       </c>
-      <c r="E33" s="32">
+      <c r="E33" s="33">
         <v>0.58</v>
       </c>
-      <c r="F33" s="32">
+      <c r="F33" s="33">
         <v>0.7</v>
       </c>
-      <c r="G33" s="32">
+      <c r="G33" s="33">
         <v>0.0</v>
       </c>
-      <c r="H33" s="32">
+      <c r="H33" s="33">
         <v>0.0</v>
       </c>
-      <c r="I33" s="32">
+      <c r="I33" s="33">
         <v>0.62</v>
       </c>
-      <c r="J33" s="32">
+      <c r="J33" s="33">
         <v>0.0</v>
       </c>
-      <c r="K33" s="32"/>
-      <c r="L33" s="32"/>
-      <c r="M33" s="32"/>
+      <c r="K33" s="33"/>
+      <c r="L33" s="33"/>
+      <c r="M33" s="33"/>
     </row>
     <row r="34" ht="15.0" customHeight="1">
-      <c r="A34" s="28" t="s">
-        <v>388</v>
-      </c>
-      <c r="B34" s="32">
+      <c r="A34" s="29" t="s">
+        <v>389</v>
+      </c>
+      <c r="B34" s="33">
         <v>0.61</v>
       </c>
-      <c r="C34" s="32">
+      <c r="C34" s="33">
         <v>0.51</v>
       </c>
-      <c r="D34" s="32">
+      <c r="D34" s="33">
         <v>0.37</v>
       </c>
-      <c r="E34" s="32">
+      <c r="E34" s="33">
         <v>0.38</v>
       </c>
-      <c r="F34" s="32">
+      <c r="F34" s="33">
         <v>0.24</v>
       </c>
-      <c r="G34" s="32"/>
-      <c r="H34" s="32"/>
-      <c r="I34" s="32"/>
-      <c r="J34" s="32"/>
-      <c r="K34" s="32"/>
-      <c r="L34" s="32"/>
-      <c r="M34" s="32"/>
+      <c r="G34" s="33"/>
+      <c r="H34" s="33"/>
+      <c r="I34" s="33"/>
+      <c r="J34" s="33"/>
+      <c r="K34" s="33"/>
+      <c r="L34" s="33"/>
+      <c r="M34" s="33"/>
     </row>
     <row r="35" ht="15.0" customHeight="1">
-      <c r="A35" s="28" t="s">
-        <v>389</v>
-      </c>
-      <c r="B35" s="32">
+      <c r="A35" s="29" t="s">
+        <v>390</v>
+      </c>
+      <c r="B35" s="33">
         <v>0.93</v>
       </c>
-      <c r="C35" s="32">
+      <c r="C35" s="33">
         <v>1.05</v>
       </c>
-      <c r="D35" s="32">
+      <c r="D35" s="33">
         <v>0.58</v>
       </c>
-      <c r="E35" s="32">
+      <c r="E35" s="33">
         <v>0.83</v>
       </c>
-      <c r="F35" s="32">
+      <c r="F35" s="33">
         <v>1.0</v>
       </c>
-      <c r="G35" s="32">
+      <c r="G35" s="33">
         <v>0.0</v>
       </c>
-      <c r="H35" s="32">
+      <c r="H35" s="33">
         <v>0.0</v>
       </c>
-      <c r="I35" s="32">
+      <c r="I35" s="33">
         <v>0.88</v>
       </c>
-      <c r="J35" s="32">
+      <c r="J35" s="33">
         <v>0.0</v>
       </c>
-      <c r="K35" s="32"/>
-      <c r="L35" s="32"/>
-      <c r="M35" s="32"/>
+      <c r="K35" s="33"/>
+      <c r="L35" s="33"/>
+      <c r="M35" s="33"/>
     </row>
     <row r="36" ht="15.0" customHeight="1">
-      <c r="A36" s="28" t="s">
-        <v>390</v>
-      </c>
-      <c r="B36" s="32">
+      <c r="A36" s="29" t="s">
+        <v>391</v>
+      </c>
+      <c r="B36" s="33">
         <v>0.87</v>
       </c>
-      <c r="C36" s="32">
+      <c r="C36" s="33">
         <v>0.74</v>
       </c>
-      <c r="D36" s="32">
+      <c r="D36" s="33">
         <v>0.53</v>
       </c>
-      <c r="E36" s="32">
+      <c r="E36" s="33">
         <v>0.55</v>
       </c>
-      <c r="F36" s="32">
+      <c r="F36" s="33">
         <v>0.34</v>
       </c>
-      <c r="G36" s="32"/>
-      <c r="H36" s="32"/>
-      <c r="I36" s="32"/>
-      <c r="J36" s="32"/>
-      <c r="K36" s="32"/>
-      <c r="L36" s="32"/>
-      <c r="M36" s="32"/>
+      <c r="G36" s="33"/>
+      <c r="H36" s="33"/>
+      <c r="I36" s="33"/>
+      <c r="J36" s="33"/>
+      <c r="K36" s="33"/>
+      <c r="L36" s="33"/>
+      <c r="M36" s="33"/>
     </row>
     <row r="37" ht="15.0" customHeight="1">
-      <c r="A37" s="26" t="s">
-        <v>391</v>
-      </c>
-      <c r="B37" s="27"/>
-      <c r="C37" s="27"/>
-      <c r="D37" s="27"/>
-      <c r="E37" s="27"/>
-      <c r="F37" s="27"/>
-      <c r="G37" s="27"/>
-      <c r="H37" s="27"/>
-      <c r="I37" s="27"/>
-      <c r="J37" s="27"/>
-      <c r="K37" s="27"/>
-      <c r="L37" s="27"/>
-      <c r="M37" s="27"/>
+      <c r="A37" s="27" t="s">
+        <v>392</v>
+      </c>
+      <c r="B37" s="28"/>
+      <c r="C37" s="28"/>
+      <c r="D37" s="28"/>
+      <c r="E37" s="28"/>
+      <c r="F37" s="28"/>
+      <c r="G37" s="28"/>
+      <c r="H37" s="28"/>
+      <c r="I37" s="28"/>
+      <c r="J37" s="28"/>
+      <c r="K37" s="28"/>
+      <c r="L37" s="28"/>
+      <c r="M37" s="28"/>
     </row>
     <row r="38" ht="15.0" customHeight="1">
-      <c r="A38" s="28" t="s">
-        <v>392</v>
-      </c>
-      <c r="B38" s="31">
+      <c r="A38" s="29" t="s">
+        <v>393</v>
+      </c>
+      <c r="B38" s="32">
         <v>6.46</v>
       </c>
-      <c r="C38" s="31">
+      <c r="C38" s="32">
         <v>5.76</v>
       </c>
-      <c r="D38" s="31">
+      <c r="D38" s="32">
         <v>5.68</v>
       </c>
-      <c r="E38" s="31">
+      <c r="E38" s="32">
         <v>3.53</v>
       </c>
-      <c r="F38" s="31">
+      <c r="F38" s="32">
         <v>2.91</v>
       </c>
-      <c r="G38" s="31">
+      <c r="G38" s="32">
         <v>4.03</v>
       </c>
-      <c r="H38" s="31">
+      <c r="H38" s="32">
         <v>2.46</v>
       </c>
-      <c r="I38" s="31">
+      <c r="I38" s="32">
         <v>1.66</v>
       </c>
-      <c r="J38" s="31">
+      <c r="J38" s="32">
         <v>2.71</v>
       </c>
-      <c r="K38" s="29"/>
-      <c r="L38" s="29"/>
-      <c r="M38" s="29"/>
+      <c r="K38" s="30"/>
+      <c r="L38" s="30"/>
+      <c r="M38" s="30"/>
     </row>
     <row r="39" ht="15.0" customHeight="1">
-      <c r="A39" s="28" t="s">
-        <v>393</v>
-      </c>
-      <c r="B39" s="31">
+      <c r="A39" s="29" t="s">
+        <v>394</v>
+      </c>
+      <c r="B39" s="32">
         <v>4.93</v>
       </c>
-      <c r="C39" s="31">
+      <c r="C39" s="32">
         <v>4.49</v>
       </c>
-      <c r="D39" s="31">
+      <c r="D39" s="32">
         <v>3.82</v>
       </c>
-      <c r="E39" s="31">
+      <c r="E39" s="32">
         <v>2.97</v>
       </c>
-      <c r="F39" s="31">
+      <c r="F39" s="32">
         <v>2.76</v>
       </c>
-      <c r="G39" s="29"/>
-      <c r="H39" s="29"/>
-      <c r="I39" s="29"/>
-      <c r="J39" s="29"/>
-      <c r="K39" s="29"/>
-      <c r="L39" s="29"/>
-      <c r="M39" s="29"/>
+      <c r="G39" s="30"/>
+      <c r="H39" s="30"/>
+      <c r="I39" s="30"/>
+      <c r="J39" s="30"/>
+      <c r="K39" s="30"/>
+      <c r="L39" s="30"/>
+      <c r="M39" s="30"/>
     </row>
     <row r="40" ht="15.0" customHeight="1">
-      <c r="A40" s="26" t="s">
-        <v>394</v>
-      </c>
-      <c r="B40" s="27"/>
-      <c r="C40" s="27"/>
-      <c r="D40" s="27"/>
-      <c r="E40" s="27"/>
-      <c r="F40" s="27"/>
-      <c r="G40" s="27"/>
-      <c r="H40" s="27"/>
-      <c r="I40" s="27"/>
-      <c r="J40" s="27"/>
-      <c r="K40" s="27"/>
-      <c r="L40" s="27"/>
-      <c r="M40" s="27"/>
+      <c r="A40" s="27" t="s">
+        <v>395</v>
+      </c>
+      <c r="B40" s="28"/>
+      <c r="C40" s="28"/>
+      <c r="D40" s="28"/>
+      <c r="E40" s="28"/>
+      <c r="F40" s="28"/>
+      <c r="G40" s="28"/>
+      <c r="H40" s="28"/>
+      <c r="I40" s="28"/>
+      <c r="J40" s="28"/>
+      <c r="K40" s="28"/>
+      <c r="L40" s="28"/>
+      <c r="M40" s="28"/>
     </row>
     <row r="41" ht="15.0" customHeight="1">
-      <c r="A41" s="28" t="s">
-        <v>395</v>
-      </c>
-      <c r="B41" s="31">
+      <c r="A41" s="29" t="s">
+        <v>396</v>
+      </c>
+      <c r="B41" s="32">
         <v>2.13</v>
       </c>
-      <c r="C41" s="31">
+      <c r="C41" s="32">
         <v>2.5</v>
       </c>
-      <c r="D41" s="31">
+      <c r="D41" s="32">
         <v>2.14</v>
       </c>
-      <c r="E41" s="31">
+      <c r="E41" s="32">
         <v>1.8</v>
       </c>
-      <c r="F41" s="31">
+      <c r="F41" s="32">
         <v>1.74</v>
       </c>
-      <c r="G41" s="31">
+      <c r="G41" s="32">
         <v>2.15</v>
       </c>
-      <c r="H41" s="31">
+      <c r="H41" s="32">
         <v>1.25</v>
       </c>
-      <c r="I41" s="31">
+      <c r="I41" s="32">
         <v>0.97</v>
       </c>
-      <c r="J41" s="31">
+      <c r="J41" s="32">
         <v>1.0</v>
       </c>
-      <c r="K41" s="29"/>
-      <c r="L41" s="29"/>
-      <c r="M41" s="29"/>
+      <c r="K41" s="30"/>
+      <c r="L41" s="30"/>
+      <c r="M41" s="30"/>
     </row>
     <row r="42" ht="15.0" customHeight="1">
-      <c r="A42" s="28" t="s">
-        <v>396</v>
-      </c>
-      <c r="B42" s="31">
+      <c r="A42" s="29" t="s">
+        <v>397</v>
+      </c>
+      <c r="B42" s="32">
         <v>2.11</v>
       </c>
-      <c r="C42" s="31">
+      <c r="C42" s="32">
         <v>2.11</v>
       </c>
-      <c r="D42" s="31">
+      <c r="D42" s="32">
         <v>1.86</v>
       </c>
-      <c r="E42" s="31">
+      <c r="E42" s="32">
         <v>1.61</v>
       </c>
-      <c r="F42" s="31">
+      <c r="F42" s="32">
         <v>1.4</v>
       </c>
-      <c r="G42" s="29"/>
-      <c r="H42" s="29"/>
-      <c r="I42" s="29"/>
-      <c r="J42" s="29"/>
-      <c r="K42" s="29"/>
-      <c r="L42" s="29"/>
-      <c r="M42" s="29"/>
+      <c r="G42" s="30"/>
+      <c r="H42" s="30"/>
+      <c r="I42" s="30"/>
+      <c r="J42" s="30"/>
+      <c r="K42" s="30"/>
+      <c r="L42" s="30"/>
+      <c r="M42" s="30"/>
     </row>
     <row r="43" ht="15.0" customHeight="1">
-      <c r="A43" s="26" t="s">
-        <v>397</v>
-      </c>
-      <c r="B43" s="27"/>
-      <c r="C43" s="27"/>
-      <c r="D43" s="27"/>
-      <c r="E43" s="27"/>
-      <c r="F43" s="27"/>
-      <c r="G43" s="27"/>
-      <c r="H43" s="27"/>
-      <c r="I43" s="27"/>
-      <c r="J43" s="27"/>
-      <c r="K43" s="27"/>
-      <c r="L43" s="27"/>
-      <c r="M43" s="27"/>
+      <c r="A43" s="27" t="s">
+        <v>398</v>
+      </c>
+      <c r="B43" s="28"/>
+      <c r="C43" s="28"/>
+      <c r="D43" s="28"/>
+      <c r="E43" s="28"/>
+      <c r="F43" s="28"/>
+      <c r="G43" s="28"/>
+      <c r="H43" s="28"/>
+      <c r="I43" s="28"/>
+      <c r="J43" s="28"/>
+      <c r="K43" s="28"/>
+      <c r="L43" s="28"/>
+      <c r="M43" s="28"/>
     </row>
     <row r="44" ht="15.0" customHeight="1">
-      <c r="A44" s="28" t="s">
-        <v>398</v>
-      </c>
-      <c r="B44" s="31">
+      <c r="A44" s="29" t="s">
+        <v>399</v>
+      </c>
+      <c r="B44" s="32">
         <v>36.49</v>
       </c>
-      <c r="C44" s="31">
+      <c r="C44" s="32">
         <v>25.98</v>
       </c>
-      <c r="D44" s="31">
+      <c r="D44" s="32">
         <v>75.26</v>
       </c>
-      <c r="E44" s="31">
+      <c r="E44" s="32">
         <v>80.35</v>
       </c>
-      <c r="F44" s="31">
+      <c r="F44" s="32">
         <v>72.14</v>
       </c>
-      <c r="G44" s="31">
+      <c r="G44" s="32">
         <v>20.31</v>
       </c>
-      <c r="H44" s="31">
+      <c r="H44" s="32">
         <v>18.8</v>
       </c>
-      <c r="I44" s="31">
+      <c r="I44" s="32">
         <v>29.8</v>
       </c>
-      <c r="J44" s="30">
+      <c r="J44" s="31">
         <v>101.76</v>
       </c>
-      <c r="K44" s="29"/>
-      <c r="L44" s="29"/>
-      <c r="M44" s="29"/>
+      <c r="K44" s="30"/>
+      <c r="L44" s="30"/>
+      <c r="M44" s="30"/>
     </row>
     <row r="45" ht="15.0" customHeight="1">
-      <c r="A45" s="28" t="s">
-        <v>399</v>
-      </c>
-      <c r="B45" s="31">
+      <c r="A45" s="29" t="s">
+        <v>400</v>
+      </c>
+      <c r="B45" s="32">
         <v>42.61</v>
       </c>
-      <c r="C45" s="31">
+      <c r="C45" s="32">
         <v>38.63</v>
       </c>
-      <c r="D45" s="31">
+      <c r="D45" s="32">
         <v>42.12</v>
       </c>
-      <c r="E45" s="31">
+      <c r="E45" s="32">
         <v>33.59</v>
       </c>
-      <c r="F45" s="31">
+      <c r="F45" s="32">
         <v>31.15</v>
       </c>
-      <c r="G45" s="29"/>
-      <c r="H45" s="29"/>
-      <c r="I45" s="29"/>
-      <c r="J45" s="29"/>
-      <c r="K45" s="29"/>
-      <c r="L45" s="29"/>
-      <c r="M45" s="29"/>
+      <c r="G45" s="30"/>
+      <c r="H45" s="30"/>
+      <c r="I45" s="30"/>
+      <c r="J45" s="30"/>
+      <c r="K45" s="30"/>
+      <c r="L45" s="30"/>
+      <c r="M45" s="30"/>
     </row>
     <row r="46" ht="15.0" customHeight="1">
-      <c r="A46" s="26" t="s">
-        <v>400</v>
-      </c>
-      <c r="B46" s="27"/>
-      <c r="C46" s="27"/>
-      <c r="D46" s="27"/>
-      <c r="E46" s="27"/>
-      <c r="F46" s="27"/>
-      <c r="G46" s="27"/>
-      <c r="H46" s="27"/>
-      <c r="I46" s="27"/>
-      <c r="J46" s="27"/>
-      <c r="K46" s="27"/>
-      <c r="L46" s="27"/>
-      <c r="M46" s="27"/>
+      <c r="A46" s="27" t="s">
+        <v>401</v>
+      </c>
+      <c r="B46" s="28"/>
+      <c r="C46" s="28"/>
+      <c r="D46" s="28"/>
+      <c r="E46" s="28"/>
+      <c r="F46" s="28"/>
+      <c r="G46" s="28"/>
+      <c r="H46" s="28"/>
+      <c r="I46" s="28"/>
+      <c r="J46" s="28"/>
+      <c r="K46" s="28"/>
+      <c r="L46" s="28"/>
+      <c r="M46" s="28"/>
     </row>
     <row r="47" ht="15.0" customHeight="1">
-      <c r="A47" s="28" t="s">
-        <v>401</v>
-      </c>
-      <c r="B47" s="31">
+      <c r="A47" s="29" t="s">
+        <v>402</v>
+      </c>
+      <c r="B47" s="32">
         <v>23.9</v>
       </c>
-      <c r="C47" s="31">
+      <c r="C47" s="32">
         <v>22.34</v>
       </c>
-      <c r="D47" s="31">
+      <c r="D47" s="32">
         <v>23.36</v>
       </c>
-      <c r="E47" s="31">
+      <c r="E47" s="32">
         <v>19.73</v>
       </c>
-      <c r="F47" s="31">
+      <c r="F47" s="32">
         <v>15.63</v>
       </c>
-      <c r="G47" s="31">
+      <c r="G47" s="32">
         <v>20.34</v>
       </c>
-      <c r="H47" s="31">
+      <c r="H47" s="32">
         <v>13.93</v>
       </c>
-      <c r="I47" s="31">
+      <c r="I47" s="32">
         <v>10.61</v>
       </c>
-      <c r="J47" s="31">
+      <c r="J47" s="32">
         <v>15.0</v>
       </c>
-      <c r="K47" s="29"/>
-      <c r="L47" s="29"/>
-      <c r="M47" s="29"/>
+      <c r="K47" s="30"/>
+      <c r="L47" s="30"/>
+      <c r="M47" s="30"/>
     </row>
     <row r="48" ht="15.0" customHeight="1">
-      <c r="A48" s="28" t="s">
-        <v>402</v>
-      </c>
-      <c r="B48" s="31">
+      <c r="A48" s="29" t="s">
+        <v>403</v>
+      </c>
+      <c r="B48" s="32">
         <v>21.55</v>
       </c>
-      <c r="C48" s="31">
+      <c r="C48" s="32">
         <v>20.8</v>
       </c>
-      <c r="D48" s="31">
+      <c r="D48" s="32">
         <v>19.28</v>
       </c>
-      <c r="E48" s="31">
+      <c r="E48" s="32">
         <v>16.53</v>
       </c>
-      <c r="F48" s="31">
+      <c r="F48" s="32">
         <v>15.36</v>
       </c>
-      <c r="G48" s="29"/>
-      <c r="H48" s="29"/>
-      <c r="I48" s="29"/>
-      <c r="J48" s="29"/>
-      <c r="K48" s="29"/>
-      <c r="L48" s="29"/>
-      <c r="M48" s="29"/>
+      <c r="G48" s="30"/>
+      <c r="H48" s="30"/>
+      <c r="I48" s="30"/>
+      <c r="J48" s="30"/>
+      <c r="K48" s="30"/>
+      <c r="L48" s="30"/>
+      <c r="M48" s="30"/>
     </row>
     <row r="49" ht="15.0" customHeight="1">
-      <c r="A49" s="26" t="s">
-        <v>403</v>
-      </c>
-      <c r="B49" s="27"/>
-      <c r="C49" s="27"/>
-      <c r="D49" s="27"/>
-      <c r="E49" s="27"/>
-      <c r="F49" s="27"/>
-      <c r="G49" s="27"/>
-      <c r="H49" s="27"/>
-      <c r="I49" s="27"/>
-      <c r="J49" s="27"/>
-      <c r="K49" s="27"/>
-      <c r="L49" s="27"/>
-      <c r="M49" s="27"/>
+      <c r="A49" s="27" t="s">
+        <v>404</v>
+      </c>
+      <c r="B49" s="28"/>
+      <c r="C49" s="28"/>
+      <c r="D49" s="28"/>
+      <c r="E49" s="28"/>
+      <c r="F49" s="28"/>
+      <c r="G49" s="28"/>
+      <c r="H49" s="28"/>
+      <c r="I49" s="28"/>
+      <c r="J49" s="28"/>
+      <c r="K49" s="28"/>
+      <c r="L49" s="28"/>
+      <c r="M49" s="28"/>
     </row>
     <row r="50" ht="15.0" customHeight="1">
-      <c r="A50" s="28" t="s">
-        <v>404</v>
-      </c>
-      <c r="B50" s="31">
+      <c r="A50" s="29" t="s">
+        <v>405</v>
+      </c>
+      <c r="B50" s="32">
         <v>57.05</v>
       </c>
-      <c r="C50" s="31">
+      <c r="C50" s="32">
         <v>37.47</v>
       </c>
-      <c r="D50" s="31">
+      <c r="D50" s="32">
         <v>38.01</v>
       </c>
-      <c r="E50" s="31">
+      <c r="E50" s="32">
         <v>32.45</v>
       </c>
-      <c r="F50" s="31">
+      <c r="F50" s="32">
         <v>24.89</v>
       </c>
-      <c r="G50" s="31">
+      <c r="G50" s="32">
         <v>35.37</v>
       </c>
-      <c r="H50" s="31">
+      <c r="H50" s="32">
         <v>31.77</v>
       </c>
-      <c r="I50" s="31">
+      <c r="I50" s="32">
         <v>19.71</v>
       </c>
-      <c r="J50" s="31">
+      <c r="J50" s="32">
         <v>38.01</v>
       </c>
-      <c r="K50" s="29"/>
-      <c r="L50" s="29"/>
-      <c r="M50" s="29"/>
+      <c r="K50" s="30"/>
+      <c r="L50" s="30"/>
+      <c r="M50" s="30"/>
     </row>
     <row r="51" ht="15.0" customHeight="1">
-      <c r="A51" s="28" t="s">
-        <v>405</v>
-      </c>
-      <c r="B51" s="31">
+      <c r="A51" s="29" t="s">
+        <v>406</v>
+      </c>
+      <c r="B51" s="32">
         <v>38.02</v>
       </c>
-      <c r="C51" s="31">
+      <c r="C51" s="32">
         <v>34.41</v>
       </c>
-      <c r="D51" s="31">
+      <c r="D51" s="32">
         <v>33.05</v>
       </c>
-      <c r="E51" s="31">
+      <c r="E51" s="32">
         <v>29.22</v>
       </c>
-      <c r="F51" s="31">
+      <c r="F51" s="32">
         <v>29.48</v>
       </c>
-      <c r="G51" s="29"/>
-      <c r="H51" s="29"/>
-      <c r="I51" s="29"/>
-      <c r="J51" s="29"/>
-      <c r="K51" s="29"/>
-      <c r="L51" s="29"/>
-      <c r="M51" s="29"/>
+      <c r="G51" s="30"/>
+      <c r="H51" s="30"/>
+      <c r="I51" s="30"/>
+      <c r="J51" s="30"/>
+      <c r="K51" s="30"/>
+      <c r="L51" s="30"/>
+      <c r="M51" s="30"/>
     </row>
     <row r="52" ht="15.0" customHeight="1">
-      <c r="A52" s="26" t="s">
-        <v>406</v>
-      </c>
-      <c r="B52" s="27"/>
-      <c r="C52" s="27"/>
-      <c r="D52" s="27"/>
-      <c r="E52" s="27"/>
-      <c r="F52" s="27"/>
-      <c r="G52" s="27"/>
-      <c r="H52" s="27"/>
-      <c r="I52" s="27"/>
-      <c r="J52" s="27"/>
-      <c r="K52" s="27"/>
-      <c r="L52" s="27"/>
-      <c r="M52" s="27"/>
+      <c r="A52" s="27" t="s">
+        <v>407</v>
+      </c>
+      <c r="B52" s="28"/>
+      <c r="C52" s="28"/>
+      <c r="D52" s="28"/>
+      <c r="E52" s="28"/>
+      <c r="F52" s="28"/>
+      <c r="G52" s="28"/>
+      <c r="H52" s="28"/>
+      <c r="I52" s="28"/>
+      <c r="J52" s="28"/>
+      <c r="K52" s="28"/>
+      <c r="L52" s="28"/>
+      <c r="M52" s="28"/>
     </row>
     <row r="53" ht="15.0" customHeight="1">
-      <c r="A53" s="28" t="s">
-        <v>407</v>
-      </c>
-      <c r="B53" s="31">
+      <c r="A53" s="29" t="s">
+        <v>408</v>
+      </c>
+      <c r="B53" s="32">
         <v>25.7</v>
       </c>
-      <c r="C53" s="31">
+      <c r="C53" s="32">
         <v>32.84</v>
       </c>
-      <c r="D53" s="31">
+      <c r="D53" s="32">
         <v>33.91</v>
       </c>
-      <c r="E53" s="31">
+      <c r="E53" s="32">
         <v>26.78</v>
       </c>
-      <c r="F53" s="31">
+      <c r="F53" s="32">
         <v>22.32</v>
       </c>
-      <c r="G53" s="31">
+      <c r="G53" s="32">
         <v>28.49</v>
       </c>
-      <c r="H53" s="31">
+      <c r="H53" s="32">
         <v>17.2</v>
       </c>
-      <c r="I53" s="31">
+      <c r="I53" s="32">
         <v>8.92</v>
       </c>
-      <c r="J53" s="31">
+      <c r="J53" s="32">
         <v>29.93</v>
       </c>
-      <c r="K53" s="29"/>
-      <c r="L53" s="29"/>
-      <c r="M53" s="29"/>
+      <c r="K53" s="30"/>
+      <c r="L53" s="30"/>
+      <c r="M53" s="30"/>
     </row>
     <row r="54" ht="15.0" customHeight="1">
-      <c r="A54" s="28" t="s">
-        <v>408</v>
-      </c>
-      <c r="B54" s="31">
+      <c r="A54" s="29" t="s">
+        <v>409</v>
+      </c>
+      <c r="B54" s="32">
         <v>4.93</v>
       </c>
-      <c r="C54" s="31">
+      <c r="C54" s="32">
         <v>4.49</v>
       </c>
-      <c r="D54" s="31">
+      <c r="D54" s="32">
         <v>3.82</v>
       </c>
-      <c r="E54" s="31">
+      <c r="E54" s="32">
         <v>2.97</v>
       </c>
-      <c r="F54" s="31">
+      <c r="F54" s="32">
         <v>2.76</v>
       </c>
-      <c r="G54" s="29"/>
-      <c r="H54" s="29"/>
-      <c r="I54" s="29"/>
-      <c r="J54" s="29"/>
-      <c r="K54" s="29"/>
-      <c r="L54" s="29"/>
-      <c r="M54" s="29"/>
+      <c r="G54" s="30"/>
+      <c r="H54" s="30"/>
+      <c r="I54" s="30"/>
+      <c r="J54" s="30"/>
+      <c r="K54" s="30"/>
+      <c r="L54" s="30"/>
+      <c r="M54" s="30"/>
     </row>
     <row r="55" ht="15.0" customHeight="1">
-      <c r="A55" s="26" t="s">
-        <v>409</v>
-      </c>
-      <c r="B55" s="27"/>
-      <c r="C55" s="27"/>
-      <c r="D55" s="27"/>
-      <c r="E55" s="27"/>
-      <c r="F55" s="27"/>
-      <c r="G55" s="27"/>
-      <c r="H55" s="27"/>
-      <c r="I55" s="27"/>
-      <c r="J55" s="27"/>
-      <c r="K55" s="27"/>
-      <c r="L55" s="27"/>
-      <c r="M55" s="27"/>
+      <c r="A55" s="27" t="s">
+        <v>410</v>
+      </c>
+      <c r="B55" s="28"/>
+      <c r="C55" s="28"/>
+      <c r="D55" s="28"/>
+      <c r="E55" s="28"/>
+      <c r="F55" s="28"/>
+      <c r="G55" s="28"/>
+      <c r="H55" s="28"/>
+      <c r="I55" s="28"/>
+      <c r="J55" s="28"/>
+      <c r="K55" s="28"/>
+      <c r="L55" s="28"/>
+      <c r="M55" s="28"/>
     </row>
     <row r="56" ht="15.0" customHeight="1">
-      <c r="A56" s="28" t="s">
-        <v>410</v>
-      </c>
-      <c r="B56" s="33">
+      <c r="A56" s="29" t="s">
+        <v>411</v>
+      </c>
+      <c r="B56" s="34">
         <v>-1.45</v>
       </c>
-      <c r="C56" s="31">
+      <c r="C56" s="32">
         <v>2.43</v>
       </c>
-      <c r="D56" s="31">
+      <c r="D56" s="32">
         <v>1.07</v>
       </c>
-      <c r="E56" s="31">
+      <c r="E56" s="32">
         <v>2.52</v>
       </c>
-      <c r="F56" s="31">
+      <c r="F56" s="32">
         <v>1.26</v>
       </c>
-      <c r="G56" s="31">
+      <c r="G56" s="32">
         <v>0.68</v>
       </c>
-      <c r="H56" s="33">
+      <c r="H56" s="34">
         <v>-3.03</v>
       </c>
-      <c r="I56" s="31">
+      <c r="I56" s="32">
         <v>1.05</v>
       </c>
-      <c r="J56" s="31">
+      <c r="J56" s="32">
         <v>0.18</v>
       </c>
-      <c r="K56" s="29"/>
-      <c r="L56" s="29"/>
-      <c r="M56" s="29"/>
+      <c r="K56" s="30"/>
+      <c r="L56" s="30"/>
+      <c r="M56" s="30"/>
     </row>
     <row r="57" ht="15.0" customHeight="1">
-      <c r="A57" s="28" t="s">
-        <v>411</v>
-      </c>
-      <c r="B57" s="31">
+      <c r="A57" s="29" t="s">
+        <v>412</v>
+      </c>
+      <c r="B57" s="32">
         <v>7.41</v>
       </c>
-      <c r="C57" s="31">
+      <c r="C57" s="32">
         <v>1.31</v>
       </c>
-      <c r="D57" s="31">
+      <c r="D57" s="32">
         <v>1.65</v>
       </c>
-      <c r="E57" s="31">
+      <c r="E57" s="32">
         <v>1.73</v>
       </c>
-      <c r="F57" s="31">
+      <c r="F57" s="32">
         <v>0.68</v>
       </c>
-      <c r="G57" s="29"/>
-      <c r="H57" s="29"/>
-      <c r="I57" s="29"/>
-      <c r="J57" s="29"/>
-      <c r="K57" s="29"/>
-      <c r="L57" s="29"/>
-      <c r="M57" s="29"/>
+      <c r="G57" s="30"/>
+      <c r="H57" s="30"/>
+      <c r="I57" s="30"/>
+      <c r="J57" s="30"/>
+      <c r="K57" s="30"/>
+      <c r="L57" s="30"/>
+      <c r="M57" s="30"/>
     </row>
     <row r="58" ht="15.0" customHeight="1">
-      <c r="A58" s="26" t="s">
-        <v>412</v>
-      </c>
-      <c r="B58" s="27"/>
-      <c r="C58" s="27"/>
-      <c r="D58" s="27"/>
-      <c r="E58" s="27"/>
-      <c r="F58" s="27"/>
-      <c r="G58" s="27"/>
-      <c r="H58" s="27"/>
-      <c r="I58" s="27"/>
-      <c r="J58" s="27"/>
-      <c r="K58" s="27"/>
-      <c r="L58" s="27"/>
-      <c r="M58" s="27"/>
+      <c r="A58" s="27" t="s">
+        <v>413</v>
+      </c>
+      <c r="B58" s="28"/>
+      <c r="C58" s="28"/>
+      <c r="D58" s="28"/>
+      <c r="E58" s="28"/>
+      <c r="F58" s="28"/>
+      <c r="G58" s="28"/>
+      <c r="H58" s="28"/>
+      <c r="I58" s="28"/>
+      <c r="J58" s="28"/>
+      <c r="K58" s="28"/>
+      <c r="L58" s="28"/>
+      <c r="M58" s="28"/>
     </row>
     <row r="59" ht="15.0" customHeight="1">
-      <c r="A59" s="28" t="s">
-        <v>413</v>
-      </c>
-      <c r="B59" s="31">
+      <c r="A59" s="29" t="s">
+        <v>414</v>
+      </c>
+      <c r="B59" s="32">
         <v>2.59</v>
       </c>
-      <c r="C59" s="31">
+      <c r="C59" s="32">
         <v>2.97</v>
       </c>
-      <c r="D59" s="31">
+      <c r="D59" s="32">
         <v>2.48</v>
       </c>
-      <c r="E59" s="31">
+      <c r="E59" s="32">
         <v>2.17</v>
       </c>
-      <c r="F59" s="31">
+      <c r="F59" s="32">
         <v>2.04</v>
       </c>
-      <c r="G59" s="31">
+      <c r="G59" s="32">
         <v>2.44</v>
       </c>
-      <c r="H59" s="31">
+      <c r="H59" s="32">
         <v>1.65</v>
       </c>
-      <c r="I59" s="31">
+      <c r="I59" s="32">
         <v>1.38</v>
       </c>
-      <c r="J59" s="31">
+      <c r="J59" s="32">
         <v>1.91</v>
       </c>
-      <c r="K59" s="29"/>
-      <c r="L59" s="29"/>
-      <c r="M59" s="29"/>
+      <c r="K59" s="30"/>
+      <c r="L59" s="30"/>
+      <c r="M59" s="30"/>
     </row>
     <row r="60" ht="15.0" customHeight="1">
-      <c r="A60" s="28" t="s">
-        <v>414</v>
-      </c>
-      <c r="B60" s="31">
+      <c r="A60" s="29" t="s">
+        <v>415</v>
+      </c>
+      <c r="B60" s="32">
         <v>2.51</v>
       </c>
-      <c r="C60" s="31">
+      <c r="C60" s="32">
         <v>2.48</v>
       </c>
-      <c r="D60" s="31">
+      <c r="D60" s="32">
         <v>2.2</v>
       </c>
-      <c r="E60" s="31">
+      <c r="E60" s="32">
         <v>1.97</v>
       </c>
-      <c r="F60" s="31">
+      <c r="F60" s="32">
         <v>1.89</v>
       </c>
-      <c r="G60" s="29"/>
-      <c r="H60" s="29"/>
-      <c r="I60" s="29"/>
-      <c r="J60" s="29"/>
-      <c r="K60" s="29"/>
-      <c r="L60" s="29"/>
-      <c r="M60" s="29"/>
+      <c r="G60" s="30"/>
+      <c r="H60" s="30"/>
+      <c r="I60" s="30"/>
+      <c r="J60" s="30"/>
+      <c r="K60" s="30"/>
+      <c r="L60" s="30"/>
+      <c r="M60" s="30"/>
     </row>
     <row r="61" ht="15.0" customHeight="1">
-      <c r="A61" s="26" t="s">
-        <v>415</v>
-      </c>
-      <c r="B61" s="27"/>
-      <c r="C61" s="27"/>
-      <c r="D61" s="27"/>
-      <c r="E61" s="27"/>
-      <c r="F61" s="27"/>
-      <c r="G61" s="27"/>
-      <c r="H61" s="27"/>
-      <c r="I61" s="27"/>
-      <c r="J61" s="27"/>
-      <c r="K61" s="27"/>
-      <c r="L61" s="27"/>
-      <c r="M61" s="27"/>
+      <c r="A61" s="27" t="s">
+        <v>416</v>
+      </c>
+      <c r="B61" s="28"/>
+      <c r="C61" s="28"/>
+      <c r="D61" s="28"/>
+      <c r="E61" s="28"/>
+      <c r="F61" s="28"/>
+      <c r="G61" s="28"/>
+      <c r="H61" s="28"/>
+      <c r="I61" s="28"/>
+      <c r="J61" s="28"/>
+      <c r="K61" s="28"/>
+      <c r="L61" s="28"/>
+      <c r="M61" s="28"/>
     </row>
     <row r="62" ht="15.0" customHeight="1">
-      <c r="A62" s="28" t="s">
-        <v>416</v>
-      </c>
-      <c r="B62" s="31">
+      <c r="A62" s="29" t="s">
+        <v>417</v>
+      </c>
+      <c r="B62" s="32">
         <v>14.32</v>
       </c>
-      <c r="C62" s="31">
+      <c r="C62" s="32">
         <v>16.55</v>
       </c>
-      <c r="D62" s="31">
+      <c r="D62" s="32">
         <v>15.66</v>
       </c>
-      <c r="E62" s="31">
+      <c r="E62" s="32">
         <v>17.8</v>
       </c>
-      <c r="F62" s="31">
+      <c r="F62" s="32">
         <v>14.2</v>
       </c>
-      <c r="G62" s="31">
+      <c r="G62" s="32">
         <v>17.32</v>
       </c>
-      <c r="H62" s="31">
+      <c r="H62" s="32">
         <v>12.91</v>
       </c>
-      <c r="I62" s="31">
+      <c r="I62" s="32">
         <v>11.31</v>
       </c>
-      <c r="J62" s="31">
+      <c r="J62" s="32">
         <v>17.42</v>
       </c>
-      <c r="K62" s="29"/>
-      <c r="L62" s="29"/>
-      <c r="M62" s="29"/>
+      <c r="K62" s="30"/>
+      <c r="L62" s="30"/>
+      <c r="M62" s="30"/>
     </row>
     <row r="63" ht="15.0" customHeight="1">
-      <c r="A63" s="28" t="s">
-        <v>417</v>
-      </c>
-      <c r="B63" s="31">
+      <c r="A63" s="29" t="s">
+        <v>418</v>
+      </c>
+      <c r="B63" s="32">
         <v>15.64</v>
       </c>
-      <c r="C63" s="31">
+      <c r="C63" s="32">
         <v>16.29</v>
       </c>
-      <c r="D63" s="31">
+      <c r="D63" s="32">
         <v>15.71</v>
       </c>
-      <c r="E63" s="31">
+      <c r="E63" s="32">
         <v>15.04</v>
       </c>
-      <c r="F63" s="31">
+      <c r="F63" s="32">
         <v>14.64</v>
       </c>
-      <c r="G63" s="29"/>
-      <c r="H63" s="29"/>
-      <c r="I63" s="29"/>
-      <c r="J63" s="29"/>
-      <c r="K63" s="29"/>
-      <c r="L63" s="29"/>
-      <c r="M63" s="29"/>
+      <c r="G63" s="30"/>
+      <c r="H63" s="30"/>
+      <c r="I63" s="30"/>
+      <c r="J63" s="30"/>
+      <c r="K63" s="30"/>
+      <c r="L63" s="30"/>
+      <c r="M63" s="30"/>
     </row>
     <row r="64" ht="15.0" customHeight="1">
-      <c r="A64" s="26" t="s">
-        <v>418</v>
-      </c>
-      <c r="B64" s="27"/>
-      <c r="C64" s="27"/>
-      <c r="D64" s="27"/>
-      <c r="E64" s="27"/>
-      <c r="F64" s="27"/>
-      <c r="G64" s="27"/>
-      <c r="H64" s="27"/>
-      <c r="I64" s="27"/>
-      <c r="J64" s="27"/>
-      <c r="K64" s="27"/>
-      <c r="L64" s="27"/>
-      <c r="M64" s="27"/>
+      <c r="A64" s="27" t="s">
+        <v>419</v>
+      </c>
+      <c r="B64" s="28"/>
+      <c r="C64" s="28"/>
+      <c r="D64" s="28"/>
+      <c r="E64" s="28"/>
+      <c r="F64" s="28"/>
+      <c r="G64" s="28"/>
+      <c r="H64" s="28"/>
+      <c r="I64" s="28"/>
+      <c r="J64" s="28"/>
+      <c r="K64" s="28"/>
+      <c r="L64" s="28"/>
+      <c r="M64" s="28"/>
     </row>
     <row r="65" ht="15.0" customHeight="1">
-      <c r="A65" s="28" t="s">
-        <v>419</v>
-      </c>
-      <c r="B65" s="31">
+      <c r="A65" s="29" t="s">
+        <v>420</v>
+      </c>
+      <c r="B65" s="32">
         <v>22.2</v>
       </c>
-      <c r="C65" s="31">
+      <c r="C65" s="32">
         <v>17.06</v>
       </c>
-      <c r="D65" s="31">
+      <c r="D65" s="32">
         <v>32.34</v>
       </c>
-      <c r="E65" s="31">
+      <c r="E65" s="32">
         <v>29.23</v>
       </c>
-      <c r="F65" s="31">
+      <c r="F65" s="32">
         <v>28.87</v>
       </c>
-      <c r="G65" s="31">
+      <c r="G65" s="32">
         <v>17.86</v>
       </c>
-      <c r="H65" s="31">
+      <c r="H65" s="32">
         <v>17.61</v>
       </c>
-      <c r="I65" s="31">
+      <c r="I65" s="32">
         <v>20.06</v>
       </c>
-      <c r="J65" s="31">
+      <c r="J65" s="32">
         <v>53.6</v>
       </c>
-      <c r="K65" s="29"/>
-      <c r="L65" s="29"/>
-      <c r="M65" s="29"/>
+      <c r="K65" s="30"/>
+      <c r="L65" s="30"/>
+      <c r="M65" s="30"/>
     </row>
     <row r="66" ht="15.0" customHeight="1">
-      <c r="A66" s="28" t="s">
-        <v>420</v>
-      </c>
-      <c r="B66" s="31">
+      <c r="A66" s="29" t="s">
+        <v>421</v>
+      </c>
+      <c r="B66" s="32">
         <v>23.37</v>
       </c>
-      <c r="C66" s="31">
+      <c r="C66" s="32">
         <v>22.8</v>
       </c>
-      <c r="D66" s="31">
+      <c r="D66" s="32">
         <v>25.33</v>
       </c>
-      <c r="E66" s="31">
+      <c r="E66" s="32">
         <v>22.41</v>
       </c>
-      <c r="F66" s="31">
+      <c r="F66" s="32">
         <v>23.15</v>
       </c>
-      <c r="G66" s="29"/>
-      <c r="H66" s="29"/>
-      <c r="I66" s="29"/>
-      <c r="J66" s="29"/>
-      <c r="K66" s="29"/>
-      <c r="L66" s="29"/>
-      <c r="M66" s="29"/>
+      <c r="G66" s="30"/>
+      <c r="H66" s="30"/>
+      <c r="I66" s="30"/>
+      <c r="J66" s="30"/>
+      <c r="K66" s="30"/>
+      <c r="L66" s="30"/>
+      <c r="M66" s="30"/>
     </row>
     <row r="67" ht="15.0" customHeight="1">
-      <c r="A67" s="26" t="s">
-        <v>421</v>
-      </c>
-      <c r="B67" s="27"/>
-      <c r="C67" s="27"/>
-      <c r="D67" s="27"/>
-      <c r="E67" s="27"/>
-      <c r="F67" s="27"/>
-      <c r="G67" s="27"/>
-      <c r="H67" s="27"/>
-      <c r="I67" s="27"/>
-      <c r="J67" s="27"/>
-      <c r="K67" s="27"/>
-      <c r="L67" s="27"/>
-      <c r="M67" s="27"/>
+      <c r="A67" s="27" t="s">
+        <v>422</v>
+      </c>
+      <c r="B67" s="28"/>
+      <c r="C67" s="28"/>
+      <c r="D67" s="28"/>
+      <c r="E67" s="28"/>
+      <c r="F67" s="28"/>
+      <c r="G67" s="28"/>
+      <c r="H67" s="28"/>
+      <c r="I67" s="28"/>
+      <c r="J67" s="28"/>
+      <c r="K67" s="28"/>
+      <c r="L67" s="28"/>
+      <c r="M67" s="28"/>
     </row>
     <row r="68" ht="15.0" customHeight="1">
-      <c r="A68" s="28" t="s">
-        <v>422</v>
-      </c>
-      <c r="B68" s="31">
+      <c r="A68" s="29" t="s">
+        <v>423</v>
+      </c>
+      <c r="B68" s="32">
         <v>44.35</v>
       </c>
-      <c r="C68" s="31">
+      <c r="C68" s="32">
         <v>30.9</v>
       </c>
-      <c r="D68" s="31">
+      <c r="D68" s="32">
         <v>87.07</v>
       </c>
-      <c r="E68" s="31">
+      <c r="E68" s="32">
         <v>96.85</v>
       </c>
-      <c r="F68" s="31">
+      <c r="F68" s="32">
         <v>84.64</v>
       </c>
-      <c r="G68" s="31">
+      <c r="G68" s="32">
         <v>23.09</v>
       </c>
-      <c r="H68" s="31">
+      <c r="H68" s="32">
         <v>24.8</v>
       </c>
-      <c r="I68" s="31">
+      <c r="I68" s="32">
         <v>42.33</v>
       </c>
-      <c r="J68" s="30">
+      <c r="J68" s="31">
         <v>193.8</v>
       </c>
-      <c r="K68" s="29"/>
-      <c r="L68" s="29"/>
-      <c r="M68" s="29"/>
+      <c r="K68" s="30"/>
+      <c r="L68" s="30"/>
+      <c r="M68" s="30"/>
     </row>
     <row r="69" ht="15.0" customHeight="1">
-      <c r="A69" s="28" t="s">
-        <v>423</v>
-      </c>
-      <c r="B69" s="31">
+      <c r="A69" s="29" t="s">
+        <v>424</v>
+      </c>
+      <c r="B69" s="32">
         <v>50.64</v>
       </c>
-      <c r="C69" s="31">
+      <c r="C69" s="32">
         <v>45.38</v>
       </c>
-      <c r="D69" s="31">
+      <c r="D69" s="32">
         <v>49.9</v>
       </c>
-      <c r="E69" s="31">
+      <c r="E69" s="32">
         <v>41.02</v>
       </c>
-      <c r="F69" s="31">
+      <c r="F69" s="32">
         <v>39.17</v>
       </c>
-      <c r="G69" s="29"/>
-      <c r="H69" s="29"/>
-      <c r="I69" s="29"/>
-      <c r="J69" s="29"/>
-      <c r="K69" s="29"/>
-      <c r="L69" s="29"/>
-      <c r="M69" s="29"/>
+      <c r="G69" s="30"/>
+      <c r="H69" s="30"/>
+      <c r="I69" s="30"/>
+      <c r="J69" s="30"/>
+      <c r="K69" s="30"/>
+      <c r="L69" s="30"/>
+      <c r="M69" s="30"/>
     </row>
     <row r="70" ht="15.75" customHeight="1"/>
     <row r="71" ht="15.75" customHeight="1"/>
